--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585722</v>
+        <v>122585771</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,26 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473371</v>
+        <v>473389</v>
       </c>
       <c r="R2" t="n">
-        <v>7140145</v>
+        <v>7140227</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585771</v>
+        <v>122585644</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +789,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,20 +810,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473389</v>
+        <v>473358</v>
       </c>
       <c r="R3" t="n">
-        <v>7140227</v>
+        <v>7140184</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +877,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585601</v>
+        <v>122585719</v>
       </c>
       <c r="B4" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +910,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473440</v>
+        <v>473453</v>
       </c>
       <c r="R4" t="n">
-        <v>7140011</v>
+        <v>7140214</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,6 +994,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585597</v>
+        <v>122585722</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1046,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473418</v>
+        <v>473371</v>
       </c>
       <c r="R5" t="n">
-        <v>7140005</v>
+        <v>7140145</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,11 +1101,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585644</v>
+        <v>122585683</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,7 +1177,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473358</v>
+        <v>473350</v>
       </c>
       <c r="R6" t="n">
-        <v>7140184</v>
+        <v>7140224</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,11 +1232,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1239,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585695</v>
+        <v>122585601</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,48 +1260,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473388</v>
+        <v>473440</v>
       </c>
       <c r="R7" t="n">
-        <v>7140077</v>
+        <v>7140011</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,11 +1334,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1356,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585659</v>
+        <v>122585695</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,16 +1366,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473399</v>
+        <v>473388</v>
       </c>
       <c r="R8" t="n">
-        <v>7140205</v>
+        <v>7140077</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,7 +1467,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585610</v>
+        <v>122585597</v>
       </c>
       <c r="B9" t="n">
         <v>57399</v>
@@ -1507,6 +1501,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1518,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473412</v>
+        <v>473418</v>
       </c>
       <c r="R9" t="n">
-        <v>7140048</v>
+        <v>7140005</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1556,6 +1555,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1564,6 +1568,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1580,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585762</v>
+        <v>122585624</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,16 +1605,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1614,11 +1623,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1630,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473437</v>
+        <v>473412</v>
       </c>
       <c r="R10" t="n">
-        <v>7140038</v>
+        <v>7140048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1668,6 +1672,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1676,11 +1685,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1697,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585719</v>
+        <v>122585659</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,16 +1717,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1747,13 +1751,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473453</v>
+        <v>473399</v>
       </c>
       <c r="R11" t="n">
-        <v>7140214</v>
+        <v>7140205</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1814,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585683</v>
+        <v>122585762</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,28 +1834,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473350</v>
+        <v>473437</v>
       </c>
       <c r="R12" t="n">
-        <v>7140224</v>
+        <v>7140038</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1914,6 +1914,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1930,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585624</v>
+        <v>122585610</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,16 +1951,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2013,11 +2018,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2039,132 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122602925</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90835</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalströmmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>473411</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7140225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla hartickor på gran i kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585771</v>
+        <v>122585601</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>97191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473389</v>
+        <v>473440</v>
       </c>
       <c r="R2" t="n">
-        <v>7140227</v>
+        <v>7140011</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585644</v>
+        <v>122585695</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +789,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,11 +810,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -822,7 +818,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473358</v>
+        <v>473388</v>
       </c>
       <c r="R3" t="n">
-        <v>7140184</v>
+        <v>7140077</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585719</v>
+        <v>122585722</v>
       </c>
       <c r="B4" t="n">
         <v>57399</v>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473453</v>
+        <v>473371</v>
       </c>
       <c r="R4" t="n">
-        <v>7140214</v>
+        <v>7140145</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585722</v>
+        <v>122585644</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1048,7 +1044,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473371</v>
+        <v>473358</v>
       </c>
       <c r="R5" t="n">
-        <v>7140145</v>
+        <v>7140184</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585683</v>
+        <v>122585624</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,36 +1148,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473350</v>
+        <v>473412</v>
       </c>
       <c r="R6" t="n">
-        <v>7140224</v>
+        <v>7140048</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,6 +1213,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585601</v>
+        <v>122585762</v>
       </c>
       <c r="B7" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1256,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473440</v>
+        <v>473437</v>
       </c>
       <c r="R7" t="n">
-        <v>7140011</v>
+        <v>7140038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,6 +1340,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1350,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585695</v>
+        <v>122585610</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1384,11 +1395,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1400,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473388</v>
+        <v>473412</v>
       </c>
       <c r="R8" t="n">
-        <v>7140077</v>
+        <v>7140048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,11 +1452,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585597</v>
+        <v>122585659</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,16 +1484,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1517,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473418</v>
+        <v>473399</v>
       </c>
       <c r="R9" t="n">
-        <v>7140005</v>
+        <v>7140205</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,11 +1554,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585624</v>
+        <v>122585719</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,16 +1601,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1623,6 +1619,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1634,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473412</v>
+        <v>473453</v>
       </c>
       <c r="R10" t="n">
-        <v>7140048</v>
+        <v>7140214</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,11 +1673,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1685,6 +1681,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1701,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585659</v>
+        <v>122585683</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,24 +1718,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1742,7 +1747,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,13 +1756,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473399</v>
+        <v>473350</v>
       </c>
       <c r="R11" t="n">
-        <v>7140205</v>
+        <v>7140224</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,11 +1802,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585762</v>
+        <v>122585597</v>
       </c>
       <c r="B12" t="n">
         <v>57399</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473437</v>
+        <v>473418</v>
       </c>
       <c r="R12" t="n">
-        <v>7140038</v>
+        <v>7140005</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,6 +1904,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585610</v>
+        <v>122585771</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1969,21 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473412</v>
+        <v>473389</v>
       </c>
       <c r="R13" t="n">
-        <v>7140048</v>
+        <v>7140227</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585644</v>
+        <v>122585624</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,19 +1044,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473358</v>
+        <v>473412</v>
       </c>
       <c r="R5" t="n">
-        <v>7140184</v>
+        <v>7140048</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,6 +1094,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1111,11 +1107,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585624</v>
+        <v>122585644</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,20 +1135,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,10 +1156,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473412</v>
+        <v>473358</v>
       </c>
       <c r="R6" t="n">
-        <v>7140048</v>
+        <v>7140184</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,11 +1215,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1228,6 +1223,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585762</v>
+        <v>122585659</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473437</v>
+        <v>473399</v>
       </c>
       <c r="R7" t="n">
-        <v>7140038</v>
+        <v>7140205</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585610</v>
+        <v>122585762</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1395,6 +1395,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473412</v>
+        <v>473437</v>
       </c>
       <c r="R8" t="n">
-        <v>7140048</v>
+        <v>7140038</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,6 +1457,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1468,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585659</v>
+        <v>122585610</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,16 +1494,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,11 +1512,6 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1518,13 +1523,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473399</v>
+        <v>473412</v>
       </c>
       <c r="R9" t="n">
-        <v>7140205</v>
+        <v>7140048</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,11 +1569,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585601</v>
+        <v>122585762</v>
       </c>
       <c r="B2" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473440</v>
+        <v>473437</v>
       </c>
       <c r="R2" t="n">
-        <v>7140011</v>
+        <v>7140038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +771,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585695</v>
+        <v>122585624</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,11 +826,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473388</v>
+        <v>473412</v>
       </c>
       <c r="R3" t="n">
-        <v>7140077</v>
+        <v>7140048</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +875,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,11 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585722</v>
+        <v>122585601</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>97194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,48 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473371</v>
+        <v>473440</v>
       </c>
       <c r="R4" t="n">
-        <v>7140145</v>
+        <v>7140011</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,11 +990,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585624</v>
+        <v>122585722</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,6 +1040,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473412</v>
+        <v>473371</v>
       </c>
       <c r="R5" t="n">
-        <v>7140048</v>
+        <v>7140145</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1094,11 +1094,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1107,6 +1102,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585644</v>
+        <v>122585659</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,20 +1135,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,11 +1156,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1168,7 +1164,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473358</v>
+        <v>473399</v>
       </c>
       <c r="R6" t="n">
-        <v>7140184</v>
+        <v>7140205</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585659</v>
+        <v>122585719</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1256,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473399</v>
+        <v>473453</v>
       </c>
       <c r="R7" t="n">
-        <v>7140205</v>
+        <v>7140214</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585762</v>
+        <v>122585597</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1411,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473437</v>
+        <v>473418</v>
       </c>
       <c r="R8" t="n">
-        <v>7140038</v>
+        <v>7140005</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585610</v>
+        <v>122585683</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,27 +1495,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1523,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473412</v>
+        <v>473350</v>
       </c>
       <c r="R9" t="n">
-        <v>7140048</v>
+        <v>7140224</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585719</v>
+        <v>122585610</v>
       </c>
       <c r="B10" t="n">
         <v>57399</v>
@@ -1619,11 +1629,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1635,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473453</v>
+        <v>473412</v>
       </c>
       <c r="R10" t="n">
-        <v>7140214</v>
+        <v>7140048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1681,11 +1686,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585683</v>
+        <v>122585771</v>
       </c>
       <c r="B11" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,48 +1718,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473350</v>
+        <v>473389</v>
       </c>
       <c r="R11" t="n">
-        <v>7140224</v>
+        <v>7140227</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1818,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585597</v>
+        <v>122585644</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,20 +1816,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1851,7 +1837,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1859,7 +1849,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,13 +1858,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473418</v>
+        <v>473358</v>
       </c>
       <c r="R12" t="n">
-        <v>7140005</v>
+        <v>7140184</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,11 +1894,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585771</v>
+        <v>122585695</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,16 +1941,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,16 +1959,26 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473389</v>
+        <v>473388</v>
       </c>
       <c r="R13" t="n">
-        <v>7140227</v>
+        <v>7140077</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2026,6 +2021,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2045,7 +2045,7 @@
         <v>122602925</v>
       </c>
       <c r="B14" t="n">
-        <v>90835</v>
+        <v>90829</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585762</v>
+        <v>122585601</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>97194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473437</v>
+        <v>473440</v>
       </c>
       <c r="R2" t="n">
-        <v>7140038</v>
+        <v>7140011</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585601</v>
+        <v>122585644</v>
       </c>
       <c r="B4" t="n">
-        <v>97194</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +905,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473440</v>
+        <v>473358</v>
       </c>
       <c r="R4" t="n">
-        <v>7140011</v>
+        <v>7140184</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,6 +989,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585722</v>
+        <v>122585762</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473371</v>
+        <v>473437</v>
       </c>
       <c r="R5" t="n">
-        <v>7140145</v>
+        <v>7140038</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585659</v>
+        <v>122585722</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,16 +1143,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473399</v>
+        <v>473371</v>
       </c>
       <c r="R6" t="n">
-        <v>7140205</v>
+        <v>7140145</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585719</v>
+        <v>122585597</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1290,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473453</v>
+        <v>473418</v>
       </c>
       <c r="R7" t="n">
-        <v>7140214</v>
+        <v>7140005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1330,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585597</v>
+        <v>122585683</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,24 +1382,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1398,7 +1411,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473418</v>
+        <v>473350</v>
       </c>
       <c r="R8" t="n">
-        <v>7140005</v>
+        <v>7140224</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1445,11 +1458,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,11 +1466,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585683</v>
+        <v>122585771</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,48 +1498,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473350</v>
+        <v>473389</v>
       </c>
       <c r="R9" t="n">
-        <v>7140224</v>
+        <v>7140227</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585610</v>
+        <v>122585659</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1629,6 +1618,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1640,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473412</v>
+        <v>473399</v>
       </c>
       <c r="R10" t="n">
-        <v>7140048</v>
+        <v>7140205</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,6 +1680,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585771</v>
+        <v>122585695</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,16 +1717,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1736,16 +1735,26 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473389</v>
+        <v>473388</v>
       </c>
       <c r="R11" t="n">
-        <v>7140227</v>
+        <v>7140077</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1788,6 +1797,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1804,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585644</v>
+        <v>122585610</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,20 +1830,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1837,19 +1851,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1858,13 +1863,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473358</v>
+        <v>473412</v>
       </c>
       <c r="R12" t="n">
-        <v>7140184</v>
+        <v>7140048</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,11 +1909,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1925,7 +1925,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585695</v>
+        <v>122585719</v>
       </c>
       <c r="B13" t="n">
         <v>57399</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473388</v>
+        <v>473453</v>
       </c>
       <c r="R13" t="n">
-        <v>7140077</v>
+        <v>7140214</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585601</v>
+        <v>122585597</v>
       </c>
       <c r="B2" t="n">
-        <v>97194</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473440</v>
+        <v>473418</v>
       </c>
       <c r="R2" t="n">
-        <v>7140011</v>
+        <v>7140005</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,6 +763,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +776,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585624</v>
+        <v>122585719</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,6 +831,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -822,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473412</v>
+        <v>473453</v>
       </c>
       <c r="R3" t="n">
-        <v>7140048</v>
+        <v>7140214</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,11 +885,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,6 +893,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585644</v>
+        <v>122585659</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +926,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,11 +947,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -934,7 +955,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473358</v>
+        <v>473399</v>
       </c>
       <c r="R4" t="n">
-        <v>7140184</v>
+        <v>7140205</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585762</v>
+        <v>122585771</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,26 +1065,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473437</v>
+        <v>473389</v>
       </c>
       <c r="R5" t="n">
-        <v>7140038</v>
+        <v>7140227</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,11 +1117,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1127,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585722</v>
+        <v>122585695</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473371</v>
+        <v>473388</v>
       </c>
       <c r="R6" t="n">
-        <v>7140145</v>
+        <v>7140077</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585597</v>
+        <v>122585601</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>97195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,48 +1262,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473418</v>
+        <v>473440</v>
       </c>
       <c r="R7" t="n">
-        <v>7140005</v>
+        <v>7140011</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,11 +1328,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1345,11 +1336,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585683</v>
+        <v>122585610</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,36 +1368,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473350</v>
+        <v>473412</v>
       </c>
       <c r="R8" t="n">
-        <v>7140224</v>
+        <v>7140048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585771</v>
+        <v>122585624</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,16 +1493,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473389</v>
+        <v>473412</v>
       </c>
       <c r="R9" t="n">
-        <v>7140227</v>
+        <v>7140048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585659</v>
+        <v>122585762</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,16 +1587,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1634,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473399</v>
+        <v>473437</v>
       </c>
       <c r="R10" t="n">
-        <v>7140205</v>
+        <v>7140038</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585695</v>
+        <v>122585644</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>57495</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,20 +1700,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1734,7 +1721,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1742,7 +1733,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473388</v>
+        <v>473358</v>
       </c>
       <c r="R11" t="n">
-        <v>7140077</v>
+        <v>7140184</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585610</v>
+        <v>122585683</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>57537</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,27 +1825,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473412</v>
+        <v>473350</v>
       </c>
       <c r="R12" t="n">
-        <v>7140048</v>
+        <v>7140224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585719</v>
+        <v>122585722</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473453</v>
+        <v>473371</v>
       </c>
       <c r="R13" t="n">
-        <v>7140214</v>
+        <v>7140145</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,7 +2045,7 @@
         <v>122602925</v>
       </c>
       <c r="B14" t="n">
-        <v>90829</v>
+        <v>90830</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585597</v>
+        <v>122585624</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,11 +709,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473418</v>
+        <v>473412</v>
       </c>
       <c r="R2" t="n">
-        <v>7140005</v>
+        <v>7140048</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -914,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585659</v>
+        <v>122585610</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,11 +938,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -964,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473399</v>
+        <v>473412</v>
       </c>
       <c r="R4" t="n">
-        <v>7140205</v>
+        <v>7140048</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,11 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585771</v>
+        <v>122585695</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,16 +1045,26 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473389</v>
+        <v>473388</v>
       </c>
       <c r="R5" t="n">
-        <v>7140227</v>
+        <v>7140077</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,6 +1107,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585695</v>
+        <v>122585644</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>57495</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1166,7 +1161,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1174,7 +1173,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473388</v>
+        <v>473358</v>
       </c>
       <c r="R6" t="n">
-        <v>7140077</v>
+        <v>7140184</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585601</v>
+        <v>122585762</v>
       </c>
       <c r="B7" t="n">
-        <v>97195</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1261,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473440</v>
+        <v>473437</v>
       </c>
       <c r="R7" t="n">
-        <v>7140011</v>
+        <v>7140038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,6 +1345,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585610</v>
+        <v>122585659</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,16 +1382,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1386,6 +1400,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1397,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473412</v>
+        <v>473399</v>
       </c>
       <c r="R8" t="n">
-        <v>7140048</v>
+        <v>7140205</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,6 +1462,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585624</v>
+        <v>122585771</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1493,21 +1517,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473412</v>
+        <v>473389</v>
       </c>
       <c r="R9" t="n">
-        <v>7140048</v>
+        <v>7140227</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,11 +1559,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585762</v>
+        <v>122585601</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>97198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,48 +1597,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473437</v>
+        <v>473440</v>
       </c>
       <c r="R10" t="n">
-        <v>7140038</v>
+        <v>7140011</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,11 +1671,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1688,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585644</v>
+        <v>122585683</v>
       </c>
       <c r="B11" t="n">
-        <v>57495</v>
+        <v>57537</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1733,7 +1732,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1742,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473358</v>
+        <v>473350</v>
       </c>
       <c r="R11" t="n">
-        <v>7140184</v>
+        <v>7140224</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,11 +1787,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1809,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585683</v>
+        <v>122585722</v>
       </c>
       <c r="B12" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,28 +1819,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1854,7 +1844,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1863,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473350</v>
+        <v>473371</v>
       </c>
       <c r="R12" t="n">
-        <v>7140224</v>
+        <v>7140145</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1909,6 +1899,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1925,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585722</v>
+        <v>122585597</v>
       </c>
       <c r="B13" t="n">
         <v>57400</v>
@@ -1975,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473371</v>
+        <v>473418</v>
       </c>
       <c r="R13" t="n">
-        <v>7140145</v>
+        <v>7140005</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2011,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,7 +2045,7 @@
         <v>122602925</v>
       </c>
       <c r="B14" t="n">
-        <v>90830</v>
+        <v>90833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585624</v>
+        <v>122585683</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473412</v>
+        <v>473350</v>
       </c>
       <c r="R2" t="n">
-        <v>7140048</v>
+        <v>7140224</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,11 +765,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585719</v>
+        <v>122585695</v>
       </c>
       <c r="B3" t="n">
         <v>57400</v>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473453</v>
+        <v>473388</v>
       </c>
       <c r="R3" t="n">
-        <v>7140214</v>
+        <v>7140077</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585610</v>
+        <v>122585659</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,6 +942,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -949,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473412</v>
+        <v>473399</v>
       </c>
       <c r="R4" t="n">
-        <v>7140048</v>
+        <v>7140205</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,6 +1004,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585695</v>
+        <v>122585610</v>
       </c>
       <c r="B5" t="n">
         <v>57400</v>
@@ -1045,11 +1059,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1061,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473388</v>
+        <v>473412</v>
       </c>
       <c r="R5" t="n">
-        <v>7140077</v>
+        <v>7140048</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,11 +1116,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585644</v>
+        <v>122585601</v>
       </c>
       <c r="B6" t="n">
-        <v>57495</v>
+        <v>97198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,51 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473358</v>
+        <v>473440</v>
       </c>
       <c r="R6" t="n">
-        <v>7140184</v>
+        <v>7140011</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,11 +1218,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1249,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585762</v>
+        <v>122585624</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,16 +1250,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1283,11 +1268,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1299,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473437</v>
+        <v>473412</v>
       </c>
       <c r="R7" t="n">
-        <v>7140038</v>
+        <v>7140048</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,6 +1317,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1345,11 +1330,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585659</v>
+        <v>122585644</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>57495</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,20 +1358,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1399,7 +1379,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1407,7 +1391,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473399</v>
+        <v>473358</v>
       </c>
       <c r="R8" t="n">
-        <v>7140205</v>
+        <v>7140184</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585771</v>
+        <v>122585722</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,16 +1483,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1517,16 +1501,26 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473389</v>
+        <v>473371</v>
       </c>
       <c r="R9" t="n">
-        <v>7140227</v>
+        <v>7140145</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,6 +1563,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1585,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585601</v>
+        <v>122585597</v>
       </c>
       <c r="B10" t="n">
-        <v>97198</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,38 +1596,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473440</v>
+        <v>473418</v>
       </c>
       <c r="R10" t="n">
-        <v>7140011</v>
+        <v>7140005</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,6 +1672,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1671,6 +1685,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1687,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585683</v>
+        <v>122585719</v>
       </c>
       <c r="B11" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,28 +1722,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1732,7 +1747,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1741,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473350</v>
+        <v>473453</v>
       </c>
       <c r="R11" t="n">
-        <v>7140224</v>
+        <v>7140214</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,6 +1802,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1803,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585722</v>
+        <v>122585771</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,16 +1839,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1837,26 +1857,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473371</v>
+        <v>473389</v>
       </c>
       <c r="R12" t="n">
-        <v>7140145</v>
+        <v>7140227</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,11 +1909,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1920,7 +1925,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585597</v>
+        <v>122585762</v>
       </c>
       <c r="B13" t="n">
         <v>57400</v>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473418</v>
+        <v>473437</v>
       </c>
       <c r="R13" t="n">
-        <v>7140005</v>
+        <v>7140038</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,11 +2011,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -1706,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585719</v>
+        <v>122585771</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1740,26 +1740,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473453</v>
+        <v>473389</v>
       </c>
       <c r="R11" t="n">
-        <v>7140214</v>
+        <v>7140227</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1802,11 +1792,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1823,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585771</v>
+        <v>122585719</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,16 +1824,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1857,16 +1842,26 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473389</v>
+        <v>473453</v>
       </c>
       <c r="R12" t="n">
-        <v>7140227</v>
+        <v>7140214</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1909,6 +1904,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585659</v>
+        <v>122585762</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473399</v>
+        <v>473437</v>
       </c>
       <c r="R2" t="n">
-        <v>7140205</v>
+        <v>7140038</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585695</v>
+        <v>122585719</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473388</v>
+        <v>473453</v>
       </c>
       <c r="R3" t="n">
-        <v>7140077</v>
+        <v>7140214</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585610</v>
+        <v>122585722</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -943,6 +943,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473412</v>
+        <v>473371</v>
       </c>
       <c r="R4" t="n">
-        <v>7140048</v>
+        <v>7140145</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +1005,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585624</v>
+        <v>122585597</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,6 +1060,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1061,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473412</v>
+        <v>473418</v>
       </c>
       <c r="R5" t="n">
-        <v>7140048</v>
+        <v>7140005</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosök tretå</t>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,6 +1127,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585771</v>
+        <v>122585659</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1162,19 +1182,29 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473389</v>
+        <v>473399</v>
       </c>
       <c r="R6" t="n">
-        <v>7140227</v>
+        <v>7140205</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,6 +1244,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585644</v>
+        <v>122585695</v>
       </c>
       <c r="B7" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,20 +1277,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1263,11 +1298,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1275,7 +1306,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473358</v>
+        <v>473388</v>
       </c>
       <c r="R7" t="n">
-        <v>7140184</v>
+        <v>7140077</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585719</v>
+        <v>122585771</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,16 +1398,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,26 +1416,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473453</v>
+        <v>473389</v>
       </c>
       <c r="R8" t="n">
-        <v>7140214</v>
+        <v>7140227</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,11 +1468,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1584,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585762</v>
+        <v>122585601</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>97309</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,48 +1612,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473437</v>
+        <v>473440</v>
       </c>
       <c r="R10" t="n">
-        <v>7140038</v>
+        <v>7140011</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,11 +1686,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1701,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585597</v>
+        <v>122585624</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,16 +1718,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1735,11 +1736,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1751,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473418</v>
+        <v>473412</v>
       </c>
       <c r="R11" t="n">
-        <v>7140005</v>
+        <v>7140048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,7 +1787,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,11 +1798,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1823,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585722</v>
+        <v>122585644</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,20 +1826,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1856,7 +1847,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1864,7 +1859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1873,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473371</v>
+        <v>473358</v>
       </c>
       <c r="R12" t="n">
-        <v>7140145</v>
+        <v>7140184</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1940,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585601</v>
+        <v>122585610</v>
       </c>
       <c r="B13" t="n">
-        <v>97301</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,38 +1947,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473440</v>
+        <v>473412</v>
       </c>
       <c r="R13" t="n">
-        <v>7140011</v>
+        <v>7140048</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,7 +2045,7 @@
         <v>122602925</v>
       </c>
       <c r="B14" t="n">
-        <v>90936</v>
+        <v>90940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585762</v>
+        <v>122585624</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,11 +709,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473437</v>
+        <v>473412</v>
       </c>
       <c r="R2" t="n">
-        <v>7140038</v>
+        <v>7140048</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,6 +758,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585719</v>
+        <v>122585610</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -826,11 +821,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473453</v>
+        <v>473412</v>
       </c>
       <c r="R3" t="n">
-        <v>7140214</v>
+        <v>7140048</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,11 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585722</v>
+        <v>122585644</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +906,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,7 +927,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -950,7 +939,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473371</v>
+        <v>473358</v>
       </c>
       <c r="R4" t="n">
-        <v>7140145</v>
+        <v>7140184</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585597</v>
+        <v>122585601</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>97309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,48 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473418</v>
+        <v>473440</v>
       </c>
       <c r="R5" t="n">
-        <v>7140005</v>
+        <v>7140011</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,11 +1093,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,11 +1101,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1265,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585695</v>
+        <v>122585762</v>
       </c>
       <c r="B7" t="n">
         <v>57494</v>
@@ -1315,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473388</v>
+        <v>473437</v>
       </c>
       <c r="R7" t="n">
-        <v>7140077</v>
+        <v>7140038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585771</v>
+        <v>122585719</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1367,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1416,16 +1385,26 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473389</v>
+        <v>473453</v>
       </c>
       <c r="R8" t="n">
-        <v>7140227</v>
+        <v>7140214</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,6 +1447,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1600,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585601</v>
+        <v>122585695</v>
       </c>
       <c r="B10" t="n">
-        <v>97309</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,38 +1596,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473440</v>
+        <v>473388</v>
       </c>
       <c r="R10" t="n">
-        <v>7140011</v>
+        <v>7140077</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1686,6 +1680,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585624</v>
+        <v>122585722</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,16 +1717,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1736,6 +1735,11 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1747,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473412</v>
+        <v>473371</v>
       </c>
       <c r="R11" t="n">
-        <v>7140048</v>
+        <v>7140145</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,11 +1789,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1798,6 +1797,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1814,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585644</v>
+        <v>122585597</v>
       </c>
       <c r="B12" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,20 +1830,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1847,11 +1851,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473358</v>
+        <v>473418</v>
       </c>
       <c r="R12" t="n">
-        <v>7140184</v>
+        <v>7140005</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,6 +1904,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585610</v>
+        <v>122585771</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1969,21 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473412</v>
+        <v>473389</v>
       </c>
       <c r="R13" t="n">
-        <v>7140048</v>
+        <v>7140227</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585624</v>
+        <v>122585771</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473412</v>
+        <v>473389</v>
       </c>
       <c r="R2" t="n">
-        <v>7140048</v>
+        <v>7140227</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585610</v>
+        <v>122585644</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +789,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,10 +810,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473412</v>
+        <v>473358</v>
       </c>
       <c r="R3" t="n">
-        <v>7140048</v>
+        <v>7140184</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +877,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585644</v>
+        <v>122585722</v>
       </c>
       <c r="B4" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,20 +910,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,11 +931,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -939,7 +939,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473358</v>
+        <v>473371</v>
       </c>
       <c r="R4" t="n">
-        <v>7140184</v>
+        <v>7140145</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585601</v>
+        <v>122585683</v>
       </c>
       <c r="B5" t="n">
-        <v>97309</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1027,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473440</v>
+        <v>473350</v>
       </c>
       <c r="R5" t="n">
-        <v>7140011</v>
+        <v>7140224</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585659</v>
+        <v>122585610</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,16 +1147,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1151,11 +1165,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1167,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473399</v>
+        <v>473412</v>
       </c>
       <c r="R6" t="n">
-        <v>7140205</v>
+        <v>7140048</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,11 +1222,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585762</v>
+        <v>122585597</v>
       </c>
       <c r="B7" t="n">
         <v>57494</v>
@@ -1284,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473437</v>
+        <v>473418</v>
       </c>
       <c r="R7" t="n">
-        <v>7140038</v>
+        <v>7140005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,6 +1324,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585719</v>
+        <v>122585762</v>
       </c>
       <c r="B8" t="n">
         <v>57494</v>
@@ -1401,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473453</v>
+        <v>473437</v>
       </c>
       <c r="R8" t="n">
-        <v>7140214</v>
+        <v>7140038</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585683</v>
+        <v>122585624</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,36 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473350</v>
+        <v>473412</v>
       </c>
       <c r="R9" t="n">
-        <v>7140224</v>
+        <v>7140048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,6 +1558,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1589,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585695</v>
+        <v>122585719</v>
       </c>
       <c r="B10" t="n">
         <v>57494</v>
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473388</v>
+        <v>473453</v>
       </c>
       <c r="R10" t="n">
-        <v>7140077</v>
+        <v>7140214</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1701,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585722</v>
+        <v>122585601</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>97311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,48 +1718,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473371</v>
+        <v>473440</v>
       </c>
       <c r="R11" t="n">
-        <v>7140145</v>
+        <v>7140011</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,11 +1792,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1818,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585597</v>
+        <v>122585659</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,16 +1824,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1868,13 +1858,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473418</v>
+        <v>473399</v>
       </c>
       <c r="R12" t="n">
-        <v>7140005</v>
+        <v>7140205</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,11 +1894,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585771</v>
+        <v>122585695</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,16 +1941,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,16 +1959,26 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473389</v>
+        <v>473388</v>
       </c>
       <c r="R13" t="n">
-        <v>7140227</v>
+        <v>7140077</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2026,6 +2021,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585771</v>
+        <v>122585644</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473389</v>
+        <v>473358</v>
       </c>
       <c r="R2" t="n">
-        <v>7140227</v>
+        <v>7140184</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,6 +775,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585644</v>
+        <v>122585610</v>
       </c>
       <c r="B3" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,19 +829,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473358</v>
+        <v>473412</v>
       </c>
       <c r="R3" t="n">
-        <v>7140184</v>
+        <v>7140048</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,11 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585722</v>
+        <v>122585771</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,26 +937,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473371</v>
+        <v>473389</v>
       </c>
       <c r="R4" t="n">
-        <v>7140145</v>
+        <v>7140227</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,11 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1131,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585610</v>
+        <v>122585719</v>
       </c>
       <c r="B6" t="n">
         <v>57494</v>
@@ -1165,6 +1155,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1176,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473412</v>
+        <v>473453</v>
       </c>
       <c r="R6" t="n">
-        <v>7140048</v>
+        <v>7140214</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,6 +1217,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585597</v>
+        <v>122585601</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>97311</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,48 +1250,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473418</v>
+        <v>473440</v>
       </c>
       <c r="R7" t="n">
-        <v>7140005</v>
+        <v>7140011</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,11 +1316,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1339,11 +1324,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1360,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585762</v>
+        <v>122585695</v>
       </c>
       <c r="B8" t="n">
         <v>57494</v>
@@ -1410,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473437</v>
+        <v>473388</v>
       </c>
       <c r="R8" t="n">
-        <v>7140038</v>
+        <v>7140077</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1589,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585719</v>
+        <v>122585762</v>
       </c>
       <c r="B10" t="n">
         <v>57494</v>
@@ -1639,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473453</v>
+        <v>473437</v>
       </c>
       <c r="R10" t="n">
-        <v>7140214</v>
+        <v>7140038</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1706,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585601</v>
+        <v>122585722</v>
       </c>
       <c r="B11" t="n">
-        <v>97311</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,38 +1698,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473440</v>
+        <v>473371</v>
       </c>
       <c r="R11" t="n">
-        <v>7140011</v>
+        <v>7140145</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,6 +1782,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1925,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585695</v>
+        <v>122585597</v>
       </c>
       <c r="B13" t="n">
         <v>57494</v>
@@ -1975,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473388</v>
+        <v>473418</v>
       </c>
       <c r="R13" t="n">
-        <v>7140077</v>
+        <v>7140005</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2011,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585659</v>
+        <v>122585597</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473399</v>
+        <v>473418</v>
       </c>
       <c r="R12" t="n">
-        <v>7140205</v>
+        <v>7140005</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,6 +1889,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585597</v>
+        <v>122585659</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,16 +1941,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1970,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473418</v>
+        <v>473399</v>
       </c>
       <c r="R13" t="n">
-        <v>7140005</v>
+        <v>7140205</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,11 +2011,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585597</v>
+        <v>122585659</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473418</v>
+        <v>473399</v>
       </c>
       <c r="R12" t="n">
-        <v>7140005</v>
+        <v>7140205</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,11 +1889,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585659</v>
+        <v>122585597</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,16 +1936,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1975,13 +1970,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473399</v>
+        <v>473418</v>
       </c>
       <c r="R13" t="n">
-        <v>7140205</v>
+        <v>7140005</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585644</v>
+        <v>122585762</v>
       </c>
       <c r="B2" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -720,7 +716,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473358</v>
+        <v>473437</v>
       </c>
       <c r="R2" t="n">
-        <v>7140184</v>
+        <v>7140038</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585610</v>
+        <v>122585624</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -877,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585771</v>
+        <v>122585601</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>97319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473389</v>
+        <v>473440</v>
       </c>
       <c r="R4" t="n">
-        <v>7140227</v>
+        <v>7140011</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585683</v>
+        <v>122585771</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,48 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473350</v>
+        <v>473389</v>
       </c>
       <c r="R5" t="n">
-        <v>7140224</v>
+        <v>7140227</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122585719</v>
+        <v>122585644</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,20 +1120,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1141,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1162,7 +1153,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1171,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473453</v>
+        <v>473358</v>
       </c>
       <c r="R6" t="n">
-        <v>7140214</v>
+        <v>7140184</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585601</v>
+        <v>122585695</v>
       </c>
       <c r="B7" t="n">
-        <v>97311</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,38 +1241,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473440</v>
+        <v>473388</v>
       </c>
       <c r="R7" t="n">
-        <v>7140011</v>
+        <v>7140077</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,6 +1325,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1340,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585695</v>
+        <v>122585610</v>
       </c>
       <c r="B8" t="n">
         <v>57494</v>
@@ -1374,11 +1380,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1390,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473388</v>
+        <v>473412</v>
       </c>
       <c r="R8" t="n">
-        <v>7140077</v>
+        <v>7140048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,11 +1437,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1457,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585624</v>
+        <v>122585719</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,16 +1469,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1491,6 +1487,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1502,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473412</v>
+        <v>473453</v>
       </c>
       <c r="R9" t="n">
-        <v>7140048</v>
+        <v>7140214</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,11 +1541,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1553,6 +1549,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585762</v>
+        <v>122585683</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,24 +1586,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1610,7 +1615,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1619,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473437</v>
+        <v>473350</v>
       </c>
       <c r="R10" t="n">
-        <v>7140038</v>
+        <v>7140224</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,11 +1670,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585722</v>
+        <v>122585659</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,16 +1702,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473371</v>
+        <v>473399</v>
       </c>
       <c r="R11" t="n">
-        <v>7140145</v>
+        <v>7140205</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585659</v>
+        <v>122585722</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473399</v>
+        <v>473371</v>
       </c>
       <c r="R12" t="n">
-        <v>7140205</v>
+        <v>7140145</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>122602925</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>90948</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585762</v>
+        <v>122585722</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473437</v>
+        <v>473371</v>
       </c>
       <c r="R2" t="n">
-        <v>7140038</v>
+        <v>7140145</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585624</v>
+        <v>122585667</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,6 +816,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473412</v>
+        <v>473373</v>
       </c>
       <c r="R3" t="n">
-        <v>7140048</v>
+        <v>7140116</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,11 +870,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök tretå</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,6 +878,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,50 +899,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585601</v>
+        <v>122585677</v>
       </c>
       <c r="B4" t="n">
-        <v>97319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473440</v>
+        <v>473351</v>
       </c>
       <c r="R4" t="n">
-        <v>7140011</v>
+        <v>7140079</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,6 +990,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122585771</v>
+        <v>122585683</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1022,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473389</v>
+        <v>473350</v>
       </c>
       <c r="R5" t="n">
-        <v>7140227</v>
+        <v>7140224</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,16 +1125,11 @@
         <v>122585644</v>
       </c>
       <c r="B6" t="n">
-        <v>57589</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1229,15 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122585695</v>
+        <v>122602925</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,32 +1249,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473388</v>
+        <v>473411</v>
       </c>
       <c r="R7" t="n">
-        <v>7140077</v>
+        <v>7140225</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,6 +1325,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla hartickor på gran i kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1328,7 +1341,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1346,19 +1359,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122585610</v>
+        <v>122585597</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1380,6 +1388,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1391,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473412</v>
+        <v>473418</v>
       </c>
       <c r="R8" t="n">
-        <v>7140048</v>
+        <v>7140005</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,6 +1442,11 @@
           <t>2025-02-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Träd med tydliga födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,6 +1455,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,19 +1476,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122585719</v>
+        <v>122585610</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1487,11 +1505,6 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1503,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473453</v>
+        <v>473412</v>
       </c>
       <c r="R9" t="n">
-        <v>7140214</v>
+        <v>7140048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,11 +1562,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1570,44 +1578,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122585683</v>
+        <v>122585695</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1615,7 +1614,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473350</v>
+        <v>473388</v>
       </c>
       <c r="R10" t="n">
-        <v>7140224</v>
+        <v>7140077</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,6 +1669,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1686,32 +1690,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122585659</v>
+        <v>122585719</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1736,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473399</v>
+        <v>473453</v>
       </c>
       <c r="R11" t="n">
-        <v>7140205</v>
+        <v>7140214</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,19 +1802,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122585722</v>
+        <v>122585762</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1853,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473371</v>
+        <v>473437</v>
       </c>
       <c r="R12" t="n">
-        <v>7140145</v>
+        <v>7140038</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,15 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122585597</v>
+        <v>122585624</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,16 +1925,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1954,11 +1943,6 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1970,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473418</v>
+        <v>473412</v>
       </c>
       <c r="R13" t="n">
-        <v>7140005</v>
+        <v>7140048</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +1994,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Träd med tydliga födosök av spillkråka.</t>
+          <t>Födosök tretå</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,11 +2005,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,15 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122602925</v>
+        <v>122585659</v>
       </c>
       <c r="B14" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,36 +2032,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2096,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473411</v>
+        <v>473399</v>
       </c>
       <c r="R14" t="n">
-        <v>7140225</v>
+        <v>7140205</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,11 +2104,6 @@
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla hartickor på gran i kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2150,7 +2115,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2165,6 +2130,200 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122585771</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalströmmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>473389</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7140227</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122585601</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalströmmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473440</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7140011</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60741-2022 artfynd.xlsx
+++ b/artfynd/A 60741-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122602925</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585597</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585610</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585695</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585719</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585722</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585762</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585624</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585659</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585667</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585677</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585771</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2111,6 +2176,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585683</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585644</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,8 +2399,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>